--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00937B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00937B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AF53344-09C5-4844-BCC6-440682A8E362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{651150E2-B5A4-43D4-8574-4724AE019AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{FC93E015-CA32-4AB1-B970-681C637F325D}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{CF3E8C60-A635-4310-AA32-5CD6B8051B2D}"/>
   </bookViews>
   <sheets>
     <sheet name="00937B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1618,24 +1618,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8EC9303-AAB8-4F14-B1D8-1FB2A0040E4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA4EFF01-72E2-4262-B377-E89F72DD709F}">
   <dimension ref="A1:R34"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1663,7 +1664,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1693,7 +1694,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1739,7 +1740,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1789,7 +1790,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1843,7 +1844,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1869,7 +1870,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1925,7 +1926,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1981,7 +1982,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2025</v>
       </c>
@@ -2035,7 +2036,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2091,7 +2092,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2147,7 +2148,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2203,7 +2204,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2259,7 +2260,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2315,7 +2316,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2371,7 +2372,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2427,7 +2428,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2483,7 +2484,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2539,7 +2540,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2595,7 +2596,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2651,7 +2652,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2707,7 +2708,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2024</v>
       </c>
@@ -2761,7 +2762,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2817,7 +2818,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2873,7 +2874,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2929,7 +2930,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2985,7 +2986,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3041,7 +3042,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3097,7 +3098,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3153,7 +3154,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>26</v>
       </c>
@@ -3209,7 +3210,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>26</v>
       </c>
@@ -3265,7 +3266,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>26</v>
       </c>
@@ -3321,7 +3322,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>26</v>
       </c>
@@ -3377,7 +3378,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="49" t="s">
         <v>77</v>
       </c>
